--- a/diamonds_42225.xlsx
+++ b/diamonds_42225.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.037145</v>
+        <v>0.036718</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.017005</v>
+        <v>0.017119</v>
       </c>
       <c r="G2" t="n">
         <v>0.619308347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.019411</v>
+        <v>0.019804</v>
       </c>
       <c r="I2" t="n">
         <v>87802482</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.032511</v>
+        <v>0.03196</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.010559</v>
+        <v>0.010627</v>
       </c>
       <c r="G3" t="n">
         <v>0.984396694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00607</v>
+        <v>0.006272</v>
       </c>
       <c r="I3" t="n">
         <v>148530357</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.032794</v>
+        <v>0.0318</v>
       </c>
       <c r="E4" t="n">
         <v>0.999815903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0125</v>
+        <v>0.01211</v>
       </c>
       <c r="G4" t="n">
         <v>0.982937091</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008521000000000001</v>
+        <v>0.008244</v>
       </c>
       <c r="I4" t="n">
         <v>148351023</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.037629</v>
+        <v>0.037369</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.020952</v>
+        <v>0.014148</v>
       </c>
       <c r="G5" t="n">
         <v>0.621338822</v>
       </c>
       <c r="H5" t="n">
-        <v>0.023622</v>
+        <v>0.021099</v>
       </c>
       <c r="I5" t="n">
         <v>87971451</v>

--- a/diamonds_42225.xlsx
+++ b/diamonds_42225.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.036718</v>
+        <v>0.037009</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.017119</v>
+        <v>0.017068</v>
       </c>
       <c r="G2" t="n">
         <v>0.619308347</v>
       </c>
       <c r="H2" t="n">
-        <v>0.019804</v>
+        <v>0.019671</v>
       </c>
       <c r="I2" t="n">
         <v>87802482</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.03196</v>
+        <v>0.032987</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.010627</v>
+        <v>0.011444</v>
       </c>
       <c r="G3" t="n">
         <v>0.984396694</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006272</v>
+        <v>0.006161</v>
       </c>
       <c r="I3" t="n">
         <v>148530357</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0318</v>
+        <v>0.032051</v>
       </c>
       <c r="E4" t="n">
         <v>0.999815903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01211</v>
+        <v>0.010458</v>
       </c>
       <c r="G4" t="n">
         <v>0.982937091</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008244</v>
+        <v>0.008263</v>
       </c>
       <c r="I4" t="n">
         <v>148351023</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.037369</v>
+        <v>0.037746</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.014148</v>
+        <v>0.01555</v>
       </c>
       <c r="G5" t="n">
         <v>0.621338822</v>
       </c>
       <c r="H5" t="n">
-        <v>0.021099</v>
+        <v>0.021332</v>
       </c>
       <c r="I5" t="n">
         <v>87971451</v>
